--- a/output/pdf_financials_xlsx/MJEM.X.xlsx
+++ b/output/pdf_financials_xlsx/MJEM.X.xlsx
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.501333</v>
+        <v>0.619207</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.936927</v>
+        <v>1.054801</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.010931</v>
+        <v>1.054801</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>1.054801</v>
@@ -3404,7 +3404,11 @@
           <t>Warrants reserve 7</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3974,7 +3978,11 @@
           <t>Warrants reserve 11</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.117874</v>
       </c>

--- a/output/pdf_financials_xlsx/MJEM.X.xlsx
+++ b/output/pdf_financials_xlsx/MJEM.X.xlsx
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.8564310000000001</v>
+        <v>2.796737</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.335947</v>
+        <v>0.736181</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.06356000000000001</v>
+        <v>0.105759</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.051282</v>
+        <v>0.102012</v>
       </c>
     </row>
     <row r="11">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.849778</v>
+        <v>-2.790084</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.06356000000000001</v>
+        <v>-0.105759</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.051282</v>
+        <v>-0.102012</v>
       </c>
     </row>
     <row r="12">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003345</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002081</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000544</v>
       </c>
     </row>
     <row r="13">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.776155</v>
+        <v>-2.7795</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.7705880000000001</v>
+        <v>-0.7726690000000001</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.105759</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.003046</v>
+        <v>-0.00359</v>
       </c>
     </row>
     <row r="28">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.772165</v>
+        <v>-2.77551</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.762624</v>
+        <v>-0.764705</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.105759</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.003046</v>
+        <v>-0.00359</v>
       </c>
     </row>
     <row r="30">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-41667.8941830753</v>
+        <v>-41718.17225311889</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.429883</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.021403</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002374</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.041943</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.033</v>
+        <v>0.462883</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.026403</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002374</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.041943</v>
       </c>
     </row>
     <row r="37">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.603697</v>
+        <v>0.173814</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.041129</v>
+        <v>0.019726</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">

--- a/output/pdf_financials_xlsx/MJEM.X.xlsx
+++ b/output/pdf_financials_xlsx/MJEM.X.xlsx
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.00399</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.007964000000000001</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">

--- a/output/pdf_financials_xlsx/MJEM.X.xlsx
+++ b/output/pdf_financials_xlsx/MJEM.X.xlsx
@@ -1669,16 +1669,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.163007</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.240245</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.220938</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.09787</v>
       </c>
     </row>
     <row r="65">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.037483</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -4628,7 +4628,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>2.344849</v>
       </c>
@@ -4834,7 +4838,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.037483</v>
       </c>
